--- a/data/trans_bre/IP19C04-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-52,11; 0,0</t>
+          <t>-53,61; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 2,91</t>
+          <t>-6,76; 2,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 10,11</t>
+          <t>-3,71; 10,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 5,74</t>
+          <t>-5,18; 5,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 8,45</t>
+          <t>-3,06; 8,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 221,57</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-54,07; 358,52</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-47,18; 319,79</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 593,97</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 944,46</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 1,19</t>
+          <t>-10,92; 0,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 4,92</t>
+          <t>-4,87; 4,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,54</t>
+          <t>-0,56; 8,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 8,39</t>
+          <t>-0,6; 8,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,23; 46,01</t>
+          <t>-84,54; 25,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,49; 170,88</t>
+          <t>-63,21; 147,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 290,47</t>
+          <t>-14,8; 276,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 421,03</t>
+          <t>-19,42; 482,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 5,42</t>
+          <t>-3,3; 5,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 4,41</t>
+          <t>-4,76; 3,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 1,68</t>
+          <t>-3,9; 1,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,35</t>
+          <t>-2,69; 3,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,62; 105,21</t>
+          <t>-37,83; 118,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,69; 128,02</t>
+          <t>-61,15; 98,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 218,92</t>
+          <t>-88,46; 234,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 263,45</t>
+          <t>-73,92; 267,35</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,87</t>
+          <t>-4,14; 1,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,84</t>
+          <t>-2,24; 3,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,03</t>
+          <t>-1,13; 3,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,14</t>
+          <t>-0,88; 3,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 32,59</t>
+          <t>-47,21; 37,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 83,87</t>
+          <t>-32,55; 80,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 159,24</t>
+          <t>-23,29; 138,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 191,18</t>
+          <t>-25,33; 155,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-53,61; 0,0</t>
+          <t>-64,61; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 2,9</t>
+          <t>-6,04; 2,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 10,85</t>
+          <t>-3,57; 9,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 5,86</t>
+          <t>-4,85; 5,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 8,73</t>
+          <t>-3,55; 9,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 221,57</t>
+          <t>-100,0; 226,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,07; 358,52</t>
+          <t>-53,2; 372,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,5; 593,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-63,82; —</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 0,92</t>
+          <t>-10,69; 1,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 4,41</t>
+          <t>-4,79; 4,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 8,97</t>
+          <t>-0,87; 9,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 8,77</t>
+          <t>-0,71; 8,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-84,54; 25,13</t>
+          <t>-83,51; 27,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-63,21; 147,32</t>
+          <t>-56,92; 142,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 276,56</t>
+          <t>-19,32; 267,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 482,37</t>
+          <t>-20,28; 426,12</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 5,98</t>
+          <t>-3,34; 5,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,72</t>
+          <t>-4,68; 4,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 1,6</t>
+          <t>-3,82; 1,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,47</t>
+          <t>-2,59; 3,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,83; 118,1</t>
+          <t>-38,36; 119,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 98,89</t>
+          <t>-56,02; 120,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,46; 234,1</t>
+          <t>-100,0; 240,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,92; 267,35</t>
+          <t>-75,07; 265,41</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,77</t>
+          <t>-4,3; 1,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,57</t>
+          <t>-2,29; 3,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,84</t>
+          <t>-0,99; 4,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,88</t>
+          <t>-0,87; 3,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 37,09</t>
+          <t>-49,46; 38,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 80,41</t>
+          <t>-31,09; 93,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 138,22</t>
+          <t>-20,74; 158,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 155,73</t>
+          <t>-23,85; 168,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-13,3</t>
+          <t>-12,08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 0,0</t>
+          <t>-49,33; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 2,87</t>
+          <t>-6,65; 2,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 9,87</t>
+          <t>-3,19; 10,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 5,9</t>
+          <t>-4,98; 5,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 9,02</t>
+          <t>-3,22; 8,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 226,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 372,63</t>
+          <t>-47,18; 319,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-84,5; 593,71</t>
+          <t>-100,0; 593,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,82; —</t>
+          <t>-71,12; 1039,25</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>104,69%</t>
+          <t>109,05%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 1,4</t>
+          <t>-10,7; 1,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,58</t>
+          <t>-4,21; 4,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 9,19</t>
+          <t>-1,05; 9,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 8,57</t>
+          <t>-1,22; 8,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-83,51; 27,59</t>
+          <t>-82,23; 46,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,92; 142,62</t>
+          <t>-57,49; 170,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 267,62</t>
+          <t>-20,49; 290,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 426,12</t>
+          <t>-33,9; 442,68</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>-15,15%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,9</t>
+          <t>-3,81; 5,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 4,29</t>
+          <t>-4,9; 4,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,63</t>
+          <t>-3,78; 1,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,74</t>
+          <t>-2,91; 1,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 119,36</t>
+          <t>-42,62; 105,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,02; 120,38</t>
+          <t>-58,69; 128,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 240,4</t>
+          <t>-89,62; 218,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,07; 265,41</t>
+          <t>-74,62; 198,4</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,9</t>
+          <t>-4,16; 1,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,86</t>
+          <t>-2,37; 3,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,07</t>
+          <t>-1,23; 4,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,76</t>
+          <t>-0,81; 3,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 38,85</t>
+          <t>-47,95; 32,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 93,91</t>
+          <t>-33,33; 83,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 158,49</t>
+          <t>-25,25; 159,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 168,21</t>
+          <t>-21,22; 171,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,161 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-12,08</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-12.08168276576544</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-49,33; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>-49.35758682716014</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,98</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-37,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>70,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,65; 2,91</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,19; 10,11</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,98; 5,74</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,22; 8,63</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-47,18; 319,79</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 593,97</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-71,12; 1039,25</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.599439995457328</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.983852724797985</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2440977548169659</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2.518888883277653</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3724274699539537</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.5163816447576611</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.06272421126043069</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.7040252820422739</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-4,8</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-51,08%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>109,05%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.651174316871246</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.19116042981417</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.984855107542592</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.21827503775231</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-0.4717682780170938</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7112132782356972</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-10,7; 1,19</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,21; 4,92</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,05; 9,54</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,22; 8,75</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-82,23; 46,01</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-57,49; 170,88</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-20,49; 290,47</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-33,9; 442,68</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.91226370558749</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.11160280838901</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.7426388889579</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>8.631504751451068</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>3.197949438633278</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>5.939655087930424</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>10.39254950135569</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +781,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-3,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-33,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-15,15%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-4.79881565611343</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.005981370132178421</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.105505206299305</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3.787125818461957</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5108108152746155</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.001100234202501503</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.7864721919081125</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1.090457827547514</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,81; 5,42</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,9; 4,41</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,78; 1,68</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,91; 1,98</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-42,62; 105,21</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-58,69; 128,02</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-89,62; 218,92</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-74,62; 198,4</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-10.69626842370662</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.208608407536929</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.050315142489195</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.217781486513076</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.8222927774241012</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5749432450178623</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.2049450430692081</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3390239230194008</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.19102045297681</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.9235321549736</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.538303946344286</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>8.751558483861945</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.4600904489485733</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.708848593966048</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.904699506810203</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>4.42682491514678</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.328933483596073</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1872193943457341</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.849612519711045</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.3928439718356952</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1886898942289352</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.03117818239313408</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.3343546960906035</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1514645312580106</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.809188249645553</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.904989409387181</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.77528150102795</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.910293126474198</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4262191050338166</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5869203349129414</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.8961975173613482</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7462004003630138</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.416565187569399</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.414088075780549</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.683486940869516</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.979701773946616</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.052093787953516</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.280212514033045</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.189168713037825</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.983975246729371</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-17,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>38,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-4,16; 1,87</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,37; 3,84</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,23; 4,03</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,81; 3,58</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-47,95; 32,59</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-33,33; 83,87</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-25,25; 159,24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-21,22; 171,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.235242497071801</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5453006366582815</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.362606974750614</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.216152037853348</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1744109336921355</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.0951364782534824</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.34774439796187</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.3885164540476794</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-4.161618589533731</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.373066499499445</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.231865662351328</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.8130009150433019</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4795010610618686</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3332610507823771</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2525376437117592</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2121568885810222</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.871085736648567</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.836824682774568</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.026638860049214</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.580337996178403</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.3259357150565209</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.8387175221282953</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.592412537469209</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.712822171241668</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1079,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
